--- a/artfynd/A 60116-2025 artfynd.xlsx
+++ b/artfynd/A 60116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130042837</v>
       </c>
       <c r="B2" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130042840</v>
       </c>
       <c r="B3" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130042845</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130042838</v>
       </c>
       <c r="B5" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>130042841</v>
       </c>
       <c r="B7" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>130042830</v>
       </c>
       <c r="B8" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>130042839</v>
       </c>
       <c r="B10" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>130042844</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130042835</v>
+        <v>130042842</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566978</v>
+        <v>566980</v>
       </c>
       <c r="R12" t="n">
-        <v>6947776</v>
+        <v>6947780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1726,11 +1726,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130042842</v>
+        <v>130042835</v>
       </c>
       <c r="B13" t="n">
-        <v>80192</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566980</v>
+        <v>566978</v>
       </c>
       <c r="R13" t="n">
-        <v>6947780</v>
+        <v>6947776</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,6 +1823,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1857,7 +1857,7 @@
         <v>130042832</v>
       </c>
       <c r="B14" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>130042829</v>
       </c>
       <c r="B15" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2048,32 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130042843</v>
+        <v>130042831</v>
       </c>
       <c r="B16" t="n">
-        <v>80228</v>
+        <v>91606</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2086,7 +2086,7 @@
         <v>566977</v>
       </c>
       <c r="R16" t="n">
-        <v>6947764</v>
+        <v>6947776</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130042831</v>
+        <v>130042843</v>
       </c>
       <c r="B17" t="n">
-        <v>91605</v>
+        <v>80229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
         <v>566977</v>
       </c>
       <c r="R17" t="n">
-        <v>6947776</v>
+        <v>6947764</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2245,7 +2245,7 @@
         <v>130042836</v>
       </c>
       <c r="B18" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60116-2025 artfynd.xlsx
+++ b/artfynd/A 60116-2025 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130042841</v>
+        <v>130042830</v>
       </c>
       <c r="B7" t="n">
-        <v>80193</v>
+        <v>91606</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567036</v>
+        <v>566970</v>
       </c>
       <c r="R7" t="n">
-        <v>6947785</v>
+        <v>6947725</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130042830</v>
+        <v>130042841</v>
       </c>
       <c r="B8" t="n">
-        <v>91606</v>
+        <v>80193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566970</v>
+        <v>567036</v>
       </c>
       <c r="R8" t="n">
-        <v>6947725</v>
+        <v>6947785</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130042844</v>
+        <v>130042835</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566965</v>
+        <v>566978</v>
       </c>
       <c r="R11" t="n">
-        <v>6947717</v>
+        <v>6947776</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130042842</v>
+        <v>130042844</v>
       </c>
       <c r="B12" t="n">
-        <v>80193</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566980</v>
+        <v>566965</v>
       </c>
       <c r="R12" t="n">
-        <v>6947780</v>
+        <v>6947717</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130042835</v>
+        <v>130042842</v>
       </c>
       <c r="B13" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566978</v>
+        <v>566980</v>
       </c>
       <c r="R13" t="n">
-        <v>6947776</v>
+        <v>6947780</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,11 +1828,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 60116-2025 artfynd.xlsx
+++ b/artfynd/A 60116-2025 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130042830</v>
+        <v>130042841</v>
       </c>
       <c r="B7" t="n">
-        <v>91606</v>
+        <v>80193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566970</v>
+        <v>567036</v>
       </c>
       <c r="R7" t="n">
-        <v>6947725</v>
+        <v>6947785</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130042841</v>
+        <v>130042830</v>
       </c>
       <c r="B8" t="n">
-        <v>80193</v>
+        <v>91606</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567036</v>
+        <v>566970</v>
       </c>
       <c r="R8" t="n">
-        <v>6947785</v>
+        <v>6947725</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 60116-2025 artfynd.xlsx
+++ b/artfynd/A 60116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130042837</v>
       </c>
       <c r="B2" t="n">
-        <v>91904</v>
+        <v>91921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130042840</v>
       </c>
       <c r="B3" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130042845</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130042838</v>
       </c>
       <c r="B5" t="n">
-        <v>91904</v>
+        <v>91921</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>130042841</v>
       </c>
       <c r="B7" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>130042830</v>
       </c>
       <c r="B8" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>130042839</v>
       </c>
       <c r="B10" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130042835</v>
+        <v>130042844</v>
       </c>
       <c r="B11" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566978</v>
+        <v>566965</v>
       </c>
       <c r="R11" t="n">
-        <v>6947776</v>
+        <v>6947717</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130042844</v>
+        <v>130042835</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566965</v>
+        <v>566978</v>
       </c>
       <c r="R12" t="n">
-        <v>6947717</v>
+        <v>6947776</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1760,7 +1760,7 @@
         <v>130042842</v>
       </c>
       <c r="B13" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>130042832</v>
       </c>
       <c r="B14" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>130042829</v>
       </c>
       <c r="B15" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>130042831</v>
       </c>
       <c r="B16" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>130042843</v>
       </c>
       <c r="B17" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>130042836</v>
       </c>
       <c r="B18" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60116-2025 artfynd.xlsx
+++ b/artfynd/A 60116-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130042833</v>
+        <v>130042838</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>91937</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567154</v>
+        <v>567007</v>
       </c>
       <c r="R5" t="n">
-        <v>6947911</v>
+        <v>6947810</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130042838</v>
+        <v>130042833</v>
       </c>
       <c r="B6" t="n">
-        <v>91937</v>
+        <v>57741</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567007</v>
+        <v>567154</v>
       </c>
       <c r="R6" t="n">
-        <v>6947810</v>
+        <v>6947911</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 60116-2025 artfynd.xlsx
+++ b/artfynd/A 60116-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130042838</v>
+        <v>130042833</v>
       </c>
       <c r="B5" t="n">
-        <v>91937</v>
+        <v>57741</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567007</v>
+        <v>567154</v>
       </c>
       <c r="R5" t="n">
-        <v>6947810</v>
+        <v>6947911</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130042833</v>
+        <v>130042838</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>91937</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567154</v>
+        <v>567007</v>
       </c>
       <c r="R6" t="n">
-        <v>6947911</v>
+        <v>6947810</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 60116-2025 artfynd.xlsx
+++ b/artfynd/A 60116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130042837</v>
       </c>
       <c r="B2" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130042833</v>
+        <v>130042838</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>91939</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567154</v>
+        <v>567007</v>
       </c>
       <c r="R5" t="n">
-        <v>6947911</v>
+        <v>6947810</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130042838</v>
+        <v>130042833</v>
       </c>
       <c r="B6" t="n">
-        <v>91937</v>
+        <v>57741</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567007</v>
+        <v>567154</v>
       </c>
       <c r="R6" t="n">
-        <v>6947810</v>
+        <v>6947911</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130042841</v>
+        <v>130042830</v>
       </c>
       <c r="B7" t="n">
-        <v>80200</v>
+        <v>91641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567036</v>
+        <v>566970</v>
       </c>
       <c r="R7" t="n">
-        <v>6947785</v>
+        <v>6947725</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130042830</v>
+        <v>130042841</v>
       </c>
       <c r="B8" t="n">
-        <v>91639</v>
+        <v>80200</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566970</v>
+        <v>567036</v>
       </c>
       <c r="R8" t="n">
-        <v>6947725</v>
+        <v>6947785</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1857,7 +1857,7 @@
         <v>130042832</v>
       </c>
       <c r="B14" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>130042829</v>
       </c>
       <c r="B15" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2048,32 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130042843</v>
+        <v>130042831</v>
       </c>
       <c r="B16" t="n">
-        <v>80236</v>
+        <v>91641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2086,7 +2086,7 @@
         <v>566977</v>
       </c>
       <c r="R16" t="n">
-        <v>6947764</v>
+        <v>6947776</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130042831</v>
+        <v>130042843</v>
       </c>
       <c r="B17" t="n">
-        <v>91639</v>
+        <v>80236</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
         <v>566977</v>
       </c>
       <c r="R17" t="n">
-        <v>6947776</v>
+        <v>6947764</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2245,7 +2245,7 @@
         <v>130042836</v>
       </c>
       <c r="B18" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 60116-2025 artfynd.xlsx
+++ b/artfynd/A 60116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130042837</v>
       </c>
       <c r="B2" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130042840</v>
       </c>
       <c r="B3" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130042845</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130042838</v>
       </c>
       <c r="B5" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130042833</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130042830</v>
+        <v>130042841</v>
       </c>
       <c r="B7" t="n">
-        <v>91641</v>
+        <v>80285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566970</v>
+        <v>567036</v>
       </c>
       <c r="R7" t="n">
-        <v>6947725</v>
+        <v>6947785</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130042841</v>
+        <v>130042830</v>
       </c>
       <c r="B8" t="n">
-        <v>80200</v>
+        <v>91728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567036</v>
+        <v>566970</v>
       </c>
       <c r="R8" t="n">
-        <v>6947785</v>
+        <v>6947725</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
         <v>130042834</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>130042839</v>
       </c>
       <c r="B10" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130042844</v>
+        <v>130042835</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566965</v>
+        <v>566978</v>
       </c>
       <c r="R11" t="n">
-        <v>6947717</v>
+        <v>6947776</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130042842</v>
+        <v>130042844</v>
       </c>
       <c r="B12" t="n">
-        <v>80200</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566980</v>
+        <v>566965</v>
       </c>
       <c r="R12" t="n">
-        <v>6947780</v>
+        <v>6947717</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130042835</v>
+        <v>130042842</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>80285</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566978</v>
+        <v>566980</v>
       </c>
       <c r="R13" t="n">
-        <v>6947776</v>
+        <v>6947780</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,11 +1828,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1857,7 +1857,7 @@
         <v>130042832</v>
       </c>
       <c r="B14" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>130042829</v>
       </c>
       <c r="B15" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2048,32 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130042831</v>
+        <v>130042843</v>
       </c>
       <c r="B16" t="n">
-        <v>91641</v>
+        <v>80321</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2086,7 +2086,7 @@
         <v>566977</v>
       </c>
       <c r="R16" t="n">
-        <v>6947776</v>
+        <v>6947764</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130042843</v>
+        <v>130042831</v>
       </c>
       <c r="B17" t="n">
-        <v>80236</v>
+        <v>91728</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
         <v>566977</v>
       </c>
       <c r="R17" t="n">
-        <v>6947764</v>
+        <v>6947776</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2245,7 +2245,7 @@
         <v>130042836</v>
       </c>
       <c r="B18" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
